--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.88421986487175</v>
+        <v>7.456185728041659</v>
       </c>
       <c r="D2" t="n">
-        <v>9.420978626544487</v>
+        <v>1.530909026813479</v>
       </c>
       <c r="E2" t="n">
-        <v>11.24782096662368</v>
+        <v>1.827770907076347</v>
       </c>
       <c r="F2" t="n">
-        <v>8.291892471412599</v>
+        <v>1.347432526604547</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.2664408223555</v>
+        <v>2.805796633632768</v>
       </c>
       <c r="D3" t="n">
-        <v>34.77021683979603</v>
+        <v>5.650160236466855</v>
       </c>
       <c r="E3" t="n">
-        <v>11.24782096662368</v>
+        <v>1.827770907076347</v>
       </c>
       <c r="F3" t="n">
-        <v>8.291892471412599</v>
+        <v>1.347432526604547</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.79432824994875</v>
+        <v>3.054078340616672</v>
       </c>
       <c r="D4" t="n">
-        <v>20.41220787395142</v>
+        <v>3.316983779517106</v>
       </c>
       <c r="E4" t="n">
-        <v>11.24782096662368</v>
+        <v>1.827770907076347</v>
       </c>
       <c r="F4" t="n">
-        <v>8.291892471412599</v>
+        <v>1.347432526604547</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.23544047937441</v>
+        <v>4.588259077898341</v>
       </c>
       <c r="D5" t="n">
-        <v>28.62397651008678</v>
+        <v>4.651396182889102</v>
       </c>
       <c r="E5" t="n">
-        <v>11.24782096662368</v>
+        <v>1.827770907076347</v>
       </c>
       <c r="F5" t="n">
-        <v>8.291892471412599</v>
+        <v>1.347432526604547</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.66486493412666</v>
+        <v>3.845540551795582</v>
       </c>
       <c r="D6" t="n">
-        <v>22.92911286325774</v>
+        <v>3.725980840279382</v>
       </c>
       <c r="E6" t="n">
-        <v>11.24782096662368</v>
+        <v>1.827770907076347</v>
       </c>
       <c r="F6" t="n">
-        <v>8.291892471412599</v>
+        <v>1.347432526604547</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.38431985869311</v>
+        <v>7.699951977037631</v>
       </c>
       <c r="D7" t="n">
-        <v>12.5926675572701</v>
+        <v>2.046308478056392</v>
       </c>
       <c r="E7" t="n">
-        <v>11.24782096662368</v>
+        <v>1.827770907076347</v>
       </c>
       <c r="F7" t="n">
-        <v>8.291892471412599</v>
+        <v>1.347432526604547</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.85757911205881</v>
+        <v>5.014356605709557</v>
       </c>
       <c r="D8" t="n">
-        <v>15.95272332121283</v>
+        <v>2.592317539697085</v>
       </c>
       <c r="E8" t="n">
-        <v>11.24782096662368</v>
+        <v>1.827770907076347</v>
       </c>
       <c r="F8" t="n">
-        <v>8.291892471412599</v>
+        <v>1.347432526604547</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
